--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table31.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table31.xlsx
@@ -205,11 +205,10 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -241,11 +240,13 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -555,7 +556,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -570,7 +571,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="15"/>
+      <c r="A1" s="14"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
@@ -580,138 +581,138 @@
       <c r="D1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="20" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="14"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="14"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16">
         <v>14.99</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="3">
+      <c r="E4" s="10"/>
+      <c r="F4" s="2">
         <v>14.99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="3">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>2.99</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18">
+      <c r="C6" s="17"/>
+      <c r="D6" s="17">
         <v>12.22</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="3">
+      <c r="E6" s="8"/>
+      <c r="F6" s="2">
         <v>15.21</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>15.76</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="3">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="2">
         <v>15.76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17">
         <v>9.99</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>35</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="3">
+      <c r="E8" s="8"/>
+      <c r="F8" s="2">
         <v>44.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17">
         <v>12</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="3">
+      <c r="D9" s="17"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>22.98</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="3">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="2">
         <v>22.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="3">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -719,161 +720,161 @@
       <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="17">
+      <c r="B13" s="1"/>
+      <c r="C13" s="16">
         <v>12.78</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="3">
+      <c r="D13" s="16"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="2">
         <v>12.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="18">
+      <c r="B14" s="1"/>
+      <c r="C14" s="17">
         <v>14.99</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="3">
+      <c r="D14" s="17"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="2">
         <v>14.99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18">
+      <c r="B15" s="1"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17">
         <v>29.99</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="3">
+      <c r="E15" s="11"/>
+      <c r="F15" s="2">
         <v>29.99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>34.269999999999996</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="3">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="2">
         <v>34.269999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>9.99</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="3">
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="2">
         <v>9.99</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="3"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="3"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="7"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>8.65</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1">
         <v>18.989999999999998</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="7">
+      <c r="E24" s="11"/>
+      <c r="F24" s="6">
         <v>27.64</v>
       </c>
     </row>
